--- a/resources/data-imports/Quests/guide-quests.xlsx
+++ b/resources/data-imports/Quests/guide-quests.xlsx
@@ -16,706 +16,2035 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="157">
-  <si>
-    <r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="336">
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">id</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">name</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">intro_text</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">instructions</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">desktop_instructions</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">mobile_instructions</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_level</t>
     </r>
   </si>
   <si>
-    <r>
+    <t>required_exploration_hours</t>
+  </si>
+  <si>
+    <t>required_training_skill</t>
+  </si>
+  <si>
+    <t>required_training_xp_sacrifice</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_reincarnation_amount</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_skill</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_skill_level</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_secondary_skill</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_secondary_skill_level</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_skill_type</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_skill_type_level</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_class_specials_equipped</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_class_rank_level</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_faction_id</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_faction_level</t>
     </r>
   </si>
   <si>
-    <r>
+    <t>faction_points_per_kill</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_game_map_id</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_quest_id</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_quest_item_id</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">secondary_quest_item_id</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_gold</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_gold_dust</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_shards</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_copper_coins</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_gold_bars</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_kingdoms</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_kingdom_level</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_kingdom_units</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_kingdom_building_id</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_kingdom_building_level</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_passive_skill</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_passive_level</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_stats</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_str</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_dex</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_agi</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_int</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_dur</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_chr</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_focus</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">gold_dust_reward</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">shards_reward</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">gold_reward</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">xp_reward</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">parent_id</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">unlock_at_level</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">only_during_event</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">be_on_game_map</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_event_goal_participation</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_event_goal_crafting_participation</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_event_goal_enchanting_participation</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_holy_stacks</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_attached_gems</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_specialty_type</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_fame_level</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_delve_survival_time</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_delve_pack_size</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_batch_crafting_type</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_batch_crafting_hours</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_item_1_source</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_item_1_name</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_item_1_type</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_item_1_amount</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_item_1_must_be_enchanted</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_item_2_source</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_item_2_name</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_item_2_type</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_item_2_amount</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_item_2_must_be_enchanted</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Manual Fighting</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">[{"id":"manual-fighting-intro","content":"Learn the basics of manual combat, then train until you reach level 2.","image_url":null}]</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">This guide uses the real combat controls. The walkthrough teaches one fight; your level remains the authoritative objective.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">[{"id":"manual-fighting-desktop","content":"Select Show me, initiate a fight, and use one manual combat action. Continue fighting until level 2, then return here to hand in the guide.","image_url":null}]</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">[{"id":"manual-fighting-mobile","content":"Tap Show me, start a fight, and use one combat action. Continue fighting until level 2, then return here to hand in the guide.","image_url":null}]</t>
     </r>
   </si>
   <si>
-    <r>
+    <t>Exploration</t>
+  </si>
+  <si>
+    <t>[{"id":"exploration-intro","content":"Learn how Exploration automatically trains your character over time, how to read its live progress and rewards, and continue exploring until you reach level 5.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>Use the real Exploration controls to start an automated session and learn how to read its live progress, rewards, currencies, and combat results. Exploration is the automated way to keep training and progressing your character. This Guide Quest completes when your character reaches level 5.</t>
+  </si>
+  <si>
+    <t>[{"id":"exploration-desktop","content":"Select Show me and follow the real Exploration setup and live panel walkthrough. After the walkthrough, let Exploration continue training your character until you reach level 5, then return here to hand in the Guide Quest.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>[{"id":"exploration-mobile","content":"Tap Show me and follow the real Exploration setup and live panel walkthrough. After the walkthrough, let Exploration continue training your character until you reach level 5, then return here to hand in the Guide Quest.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>Manual Fighting</t>
+  </si>
+  <si>
+    <t>Training Skill</t>
+  </si>
+  <si>
+    <t>[{"id":"training-skill-intro","content":"Learn how Training Skills redirect part of your earned character XP into a skill. Train Accuracy at 10% and raise Accuracy to level 3.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>Use the Character Sheet Training Skills flow to train Accuracy with a 10% XP sacrifice. While Accuracy is training, 10% of earned character XP is redirected into the skill. Keep Accuracy training at 10% until it reaches level 3. Exploration is recommended because its automated fights continue earning character XP that feeds your training skill.</t>
+  </si>
+  <si>
+    <t>[{"id":"training-skill-desktop","content":"Select Show me and follow the Training Skills walkthrough. Start training Accuracy at 10%, then use Exploration or normal combat to keep earning XP until Accuracy reaches level 3.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>[{"id":"training-skill-mobile","content":"Tap Show me and follow the Training Skills walkthrough. Start training Accuracy at 10%, then use Exploration or normal combat to keep earning XP until Accuracy reaches level 3.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Factions</t>
+  </si>
+  <si>
+    <t>[{"id":"factions-intro","content":"Learn how Factions track your progress across the major planes. Raise your Surface Faction to level 3 while learning what Faction levels unlock and how they are used by later progression systems.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>Factions represent your standing on the major planes. Killing monsters earns Faction points for the plane you are fighting on, and some Quests require specific Faction levels before you can continue. Mastering a Faction later allows you to pledge to it and unlock Faction Loyalty. For this Guide Quest, raise Surface to level 3. You have a bonus of +25 faction points per kill until Surface reaches level 3.</t>
+  </si>
+  <si>
+    <t>[{"id":"factions-desktop","content":"Select Show me to learn the Factions screen and Surface progress. Then keep killing monsters manually or through Exploration until Surface reaches level 3. Watch Server Messages during fight rewards for Faction points and Faction level-up messages.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>[{"id":"factions-mobile","content":"Tap Show me to learn the Factions screen and Surface progress. Then keep killing monsters manually or through Exploration until Surface reaches level 3. Watch Server Messages during fight rewards for Faction points and Faction level-up messages.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Inventory &amp; Character Sheet</t>
+  </si>
+  <si>
+    <t>[{"id":"inventory-character-sheet-intro","content":"Learn how your Backpack, equipment, Sets, Alchemy items, Gems, and Character Sheet work together. Reach level 10 with every core modified stat at 50 or higher.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>Improve and equip the gear and Gems you find while progressing. Modified stats are the source of truth: all seven must be at least 50 and the character must be level 10.</t>
+  </si>
+  <si>
+    <t>[{"id":"inventory-and-character-sheet-desktop","content":"Use Show me, follow the real interface steps, then continue progressing until the requirement is met.","image_url":null}]</t>
+  </si>
+  <si>
+    <t>[{"id":"inventory-and-character-sheet-mobile","content":"Tap Show me, follow the real interface steps, then continue progressing until the requirement is met.","image_url":null}]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">guide_quest_name</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">position</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">title</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">content</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">target</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">step_type</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">required_event</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">optional_if_target_missing</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Start a Fight</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Select Initiate Fight to begin a real manual battle.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">manual-fight-initiate</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">event</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">fight-started</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Choose a Combat Action</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Manual fights normally give you Attack, Cast, mixed attack/cast, and Defend actions here. Use one if the creature survives the opening action.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">manual-fight-actions</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">combat-action-succeeded</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Read Battle Feedback</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Battle Messages show the immediate result of the current fight, including damage and combat outcomes.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">battle-messages</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">continue</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Open Server Messages</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Server Messages records broader game outcomes such as rewards, drops, progression notices, and errors. Open it now.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">server-messages-tab</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">click</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Understand Server Messages</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">This is your Server Messages history. Equipment drops and special quest-item drops can appear here as clickable messages.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">server-messages-panel</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Quest Item Drop</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Quest items are special progression items, not normal equipment. If one dropped, open its message to inspect it.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">server-message-quest-item</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Quest Item Details</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Quest items can unlock travel, quests, locations, progression, or other game systems. Their detail view explains what the item is connected to.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">quest-item-details</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Return to Server Messages</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Close the quest-item panel to return to Server Messages.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">side-peek-close</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Equipment Drop</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Normal equipment drops are different from quest items. If one dropped, open the equipment message now.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">server-message-item</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Understand the Item</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">This is the real item detail view. It shows the item type, enchantments, combat values, stat bonuses, and the actions available for the item.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">item-details</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Review Item Stats</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">These values show the bonuses and penalties the item contributes when equipped.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">item-stats</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Inspect an Enchantment</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Equipment may have a prefix or suffix enchantment. If this item has one, open it to see exactly what that enchantment contributes.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">item-affixes</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Understand the Enchantment</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">This view breaks down the selected prefix or suffix: its description, stat changes, damage modifiers, skill effects, and other bonuses.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">item-affix-details</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Back to the Item</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Close the enchantment detail to return to the item.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">item-affix-close</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Open Item Actions</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Open Actions to see what else can be done with an equipment item.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">item-actions</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Understand Item Actions</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Actions contains non-equip operations such as moving the item to a set, selling, listing, destroying, or disenchanting it.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Equip the Item</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">Choose Equip Item to compare this drop against what you currently have equipped.</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
       <t xml:space="preserve">item-equip-action</t>
     </r>
   </si>
   <si>
-    <t>Manual Fighting</t>
-  </si>
-  <si>
     <t>Compare the Equipment</t>
   </si>
   <si>
@@ -752,19 +2081,478 @@
     <t>item-equipped</t>
   </si>
   <si>
+    <t>Item Equipped</t>
+  </si>
+  <si>
+    <t>The item detail has refreshed from the server and now shows that this item is Equipped. The stale Equip Item action is no longer available.</t>
+  </si>
+  <si>
+    <t>item-equipped-state</t>
+  </si>
+  <si>
+    <t>Keep Training</t>
+  </si>
+  <si>
     <t>Continue fighting normally until level 2, then return to the Guide Quest and hand it in. You can use Show me again at any time to replay this walkthrough from the beginning.</t>
   </si>
   <si>
-    <t>Keep Training</t>
-  </si>
-  <si>
-    <t>Item Equipped</t>
-  </si>
-  <si>
-    <t>The item detail has refreshed from the server and now shows that this item is Equipped. The stale Equip Item action is no longer available.</t>
-  </si>
-  <si>
-    <t>item-equipped-state</t>
+    <t>Open Exploration</t>
+  </si>
+  <si>
+    <t>Open Exploration from the fight screen. Exploration lets the game fight automatically for your character over a selected period of time.</t>
+  </si>
+  <si>
+    <t>exploration-open</t>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
+    <t>Choose a Monster</t>
+  </si>
+  <si>
+    <t>Choose the monster you want Exploration to fight automatically.</t>
+  </si>
+  <si>
+    <t>exploration-monster</t>
+  </si>
+  <si>
+    <t>Choose One Hour</t>
+  </si>
+  <si>
+    <t>Choose One Hour for this walkthrough. The Guide Quest no longer requires you to complete the full hour; this simply starts a normal Exploration session you can continue using to train your character.</t>
+  </si>
+  <si>
+    <t>exploration-duration</t>
+  </si>
+  <si>
+    <t>Choose an Attack Type</t>
+  </si>
+  <si>
+    <t>Choose the attack type Exploration should use during its automated fights.</t>
+  </si>
+  <si>
+    <t>exploration-attack-type</t>
+  </si>
+  <si>
+    <t>Begin Exploration</t>
+  </si>
+  <si>
+    <t>Start Exploration. Your character will now fight automatically using the monster, duration, and attack type you selected.</t>
+  </si>
+  <si>
+    <t>exploration-begin</t>
+  </si>
+  <si>
+    <t>Live Exploration</t>
+  </si>
+  <si>
+    <t>This is your live Exploration panel. Status shows what Exploration is doing, which attack type is being used, how long it has been running, and the current monster. Character Progress shows your current level progress and the currencies your character currently holds.</t>
+  </si>
+  <si>
+    <t>exploration-live-panel</t>
+  </si>
+  <si>
+    <t>Exploration Messages</t>
+  </si>
+  <si>
+    <t>Open Exploration Messages. This stream shows the automated combat activity produced while Exploration is running.</t>
+  </si>
+  <si>
+    <t>exploration-messages-tab</t>
+  </si>
+  <si>
+    <t>Server Messages</t>
+  </si>
+  <si>
+    <t>Open Server Messages. This is where broader game results appear, including rewards, equipment drops, currencies, progression notices, and other important outcomes from your Exploration fights.</t>
+  </si>
+  <si>
+    <t>server-messages-tab</t>
+  </si>
+  <si>
+    <t>Exploration Progress</t>
+  </si>
+  <si>
+    <t>Exploration Progress tracks the fights and kills completed during this session along with character XP, Skill XP, and faction points earned. Select the Breakdown tab to see the totals instead of the chart.</t>
+  </si>
+  <si>
+    <t>exploration-progress</t>
+  </si>
+  <si>
+    <t>Currencies Gained</t>
+  </si>
+  <si>
+    <t>Currencies Gained tracks the currencies rewarded during Exploration. Select the Breakdown tab to see the totals. If no encounter has rewarded currency yet, the section will show an empty state until rewards arrive.</t>
+  </si>
+  <si>
+    <t>exploration-currencies</t>
+  </si>
+  <si>
+    <t>Combat Summary</t>
+  </si>
+  <si>
+    <t>Combat Summary tracks the damage, healing, and blocked damage produced by your automated fights. Select the Breakdown tab to see the totals for the current Exploration session.</t>
+  </si>
+  <si>
+    <t>exploration-combat-summary</t>
+  </si>
+  <si>
+    <t>Keep Exploring</t>
+  </si>
+  <si>
+    <t>Exploration will continue automatically. As you explore you will gain character XP, Skill XP, gear, currencies, faction points, and other rewards. Exploration is the automated way to keep training and progressing your character. Continue until you reach level 5, then return to the Guide Quest and hand it in.</t>
+  </si>
+  <si>
+    <t>Open Character</t>
+  </si>
+  <si>
+    <t>Open Character to begin learning where your character information and Training Skills are managed.</t>
+  </si>
+  <si>
+    <t>character-open</t>
+  </si>
+  <si>
+    <t>Character Summary</t>
+  </si>
+  <si>
+    <t>This floating Character card is your quick character summary. It shows your XP progress, modified stats, combat values, currencies, inventory access, and other useful character information without leaving the fight screen.</t>
+  </si>
+  <si>
+    <t>character-card-overview</t>
+  </si>
+  <si>
+    <t>See More Details</t>
+  </si>
+  <si>
+    <t>Select See More Details to open the full Character Sheet, where you can inspect your character in more detail and manage systems such as Skills.</t>
+  </si>
+  <si>
+    <t>character-more-details</t>
+  </si>
+  <si>
+    <t>Your Character Sheet</t>
+  </si>
+  <si>
+    <t>This is the full Character Sheet. It contains your character information, currencies, combat values, modified stats, elemental values, and management options. You can return here whenever you want a detailed view of how your character is built.</t>
+  </si>
+  <si>
+    <t>character-sheet-overview</t>
+  </si>
+  <si>
+    <t>Manage Skills</t>
+  </si>
+  <si>
+    <t>Select Manage Skills to open your character's Training Skills and Crafting Skills.</t>
+  </si>
+  <si>
+    <t>character-skills</t>
+  </si>
+  <si>
+    <t>Skill Categories</t>
+  </si>
+  <si>
+    <t>There are two skill categories here. Training Skills improve by redirecting part of the character XP you earn into one selected skill. Crafting Skills progress through their related crafting activities.</t>
+  </si>
+  <si>
+    <t>skills-overview</t>
+  </si>
+  <si>
+    <t>Training Skills</t>
+  </si>
+  <si>
+    <t>Training Skills is already selected. Only one Training Skill can be actively trained at a time. For this Guide Quest, you are going to train Accuracy.</t>
+  </si>
+  <si>
+    <t>training-skills-tab</t>
+  </si>
+  <si>
+    <t>Open Accuracy</t>
+  </si>
+  <si>
+    <t>Select Accuracy to see how the skill works and begin training it.</t>
+  </si>
+  <si>
+    <t>accuracy-skill</t>
+  </si>
+  <si>
+    <t>These are the details for Accuracy. Level shows its current progression. Skill Bonus improves the skill's effectiveness, Skill XP Bonus increases the XP it receives while training, and the Skill XP bar shows progress toward its next level. This Guide Quest requires Accuracy to reach level 3.</t>
+  </si>
+  <si>
+    <t>skill-facts</t>
+  </si>
+  <si>
+    <t>Training Accuracy</t>
+  </si>
+  <si>
+    <t>This Training section controls how much earned character XP is redirected into Accuracy. Training does not create extra XP; it redirects part of the XP your character earns into the selected Training Skill.</t>
+  </si>
+  <si>
+    <t>skill-training-section</t>
+  </si>
+  <si>
+    <t>Choose 10%</t>
+  </si>
+  <si>
+    <t>Open the XP percentage selector and choose 10%. Accuracy must be actively training at a 10% XP sacrifice for this Guide Quest.</t>
+  </si>
+  <si>
+    <t>skill-training-percentage</t>
+  </si>
+  <si>
+    <t>What 10% Means</t>
+  </si>
+  <si>
+    <t>With 10% selected, 10% of the character XP you earn will be redirected into Accuracy. The remaining 90% continues progressing your character normally. Only one Training Skill can receive this redirected XP at a time.</t>
+  </si>
+  <si>
+    <t>skill-xp-sacrifice-help</t>
+  </si>
+  <si>
+    <t>Start Training Accuracy</t>
+  </si>
+  <si>
+    <t>Select Train Skill now. The walkthrough will continue only after the game confirms that Accuracy is actively training at 10%.</t>
+  </si>
+  <si>
+    <t>skill-training-submit</t>
+  </si>
+  <si>
+    <t>skill-training-started</t>
+  </si>
+  <si>
+    <t>Accuracy Is Training</t>
+  </si>
+  <si>
+    <t>Accuracy is now actively training at 10%. As you earn character XP, part of that XP will now feed Accuracy. Next, look at the items that can improve how this skill performs and trains.</t>
+  </si>
+  <si>
+    <t>Items Affecting Accuracy</t>
+  </si>
+  <si>
+    <t>Items Affecting This Skill shows equipped items and quest items that modify Accuracy. Skill Bonus improves Accuracy itself, while Skill XP Bonus increases how much training XP Accuracy receives.</t>
+  </si>
+  <si>
+    <t>skill-items-affecting</t>
+  </si>
+  <si>
+    <t>Open an Accuracy Quest Item</t>
+  </si>
+  <si>
+    <t>If a quest item is affecting Accuracy, select it now to see the bonuses it contributes to the skill.</t>
+  </si>
+  <si>
+    <t>skill-quest-item</t>
+  </si>
+  <si>
+    <t>Quest Item Skill Bonuses</t>
+  </si>
+  <si>
+    <t>This quest item contributes directly to Accuracy. Skill Bonus improves the skill's effectiveness, while Skill XP Bonus increases the XP Accuracy receives while it is training.</t>
+  </si>
+  <si>
+    <t>skill-quest-item-details</t>
+  </si>
+  <si>
+    <t>Close Quest Item Details</t>
+  </si>
+  <si>
+    <t>Close the quest-item details to return to Accuracy.</t>
+  </si>
+  <si>
+    <t>skill-quest-item-close</t>
+  </si>
+  <si>
+    <t>Keep Training Accuracy</t>
+  </si>
+  <si>
+    <t>Accuracy is now training at 10%. Use Exploration to keep earning character XP automatically until Accuracy reaches level 3. Accuracy level 3 while training at 10% is the requirement for this Guide Quest.</t>
+  </si>
+  <si>
+    <t>Open Map</t>
+  </si>
+  <si>
+    <t>Open Map. Factions are accessed from the Map card because each normal Faction belongs to one of the major planes.</t>
+  </si>
+  <si>
+    <t>map-open</t>
+  </si>
+  <si>
+    <t>Open Factions</t>
+  </si>
+  <si>
+    <t>Select Factions. The walkthrough will scroll to the Factions button for you.</t>
+  </si>
+  <si>
+    <t>map-factions</t>
+  </si>
+  <si>
+    <t>What Are Factions?</t>
+  </si>
+  <si>
+    <t>Factions track your standing on the major planes. Killing monsters on a plane earns Faction points for that plane. Faction levels are used as progression gates, and some Quests require specific Faction levels before you can continue. Once a Faction is mastered, you can later pledge to it and unlock the deeper Faction Loyalty system.</t>
+  </si>
+  <si>
+    <t>factions-overview</t>
+  </si>
+  <si>
+    <t>Open Surface</t>
+  </si>
+  <si>
+    <t>Select the Surface Faction. Surface is the Faction you will progress for this Guide Quest.</t>
+  </si>
+  <si>
+    <t>surface-faction</t>
+  </si>
+  <si>
+    <t>Surface Faction Progress</t>
+  </si>
+  <si>
+    <t>This screen shows your Surface Faction level, current Faction points, the points needed for the next level, your Faction title, and whether the Faction is mastered. For this Guide Quest, Surface must reach level 3. Faction Loyalty comes later after you have progressed and mastered a Faction.</t>
+  </si>
+  <si>
+    <t>faction-detail-overview</t>
+  </si>
+  <si>
+    <t>Return to Combat</t>
+  </si>
+  <si>
+    <t>Close the Map card and return to combat. You now know where to check your Faction progress.</t>
+  </si>
+  <si>
+    <t>map-close</t>
+  </si>
+  <si>
+    <t>Open Server Messages</t>
+  </si>
+  <si>
+    <t>Open Server Messages. Faction rewards are reported during the reward phase of fights, and this is where you can see Faction point gains and messages when your Faction reaches a new level.</t>
+  </si>
+  <si>
+    <t>Faction Rewards</t>
+  </si>
+  <si>
+    <t>Server Messages records your fight rewards. As you kill monsters, watch here for Faction point gains and Faction level-up messages. While this Guide Quest is active, Surface receives an additional +25 faction points per kill until it reaches level 3.</t>
+  </si>
+  <si>
+    <t>server-messages-panel</t>
+  </si>
+  <si>
+    <t>Reach Surface Level 3</t>
+  </si>
+  <si>
+    <t>Keep killing monsters manually or through Exploration until your Surface Faction reaches level 3. You have +25 bonus faction points per kill until you reach that requirement. Check Server Messages during fight rewards to see your Faction progress and Faction level-ups.</t>
+  </si>
+  <si>
+    <t>Follow this step through the existing game interface.</t>
+  </si>
+  <si>
+    <t>Manage Inventory</t>
+  </si>
+  <si>
+    <t>character-manage-inventory</t>
+  </si>
+  <si>
+    <t>Equipment and Inventory</t>
+  </si>
+  <si>
+    <t>character-inventory</t>
+  </si>
+  <si>
+    <t>Your Equipped Gear</t>
+  </si>
+  <si>
+    <t>inventory-equipped-item</t>
+  </si>
+  <si>
+    <t>Open Backpack</t>
+  </si>
+  <si>
+    <t>inventory-backpack</t>
+  </si>
+  <si>
+    <t>Backpack</t>
+  </si>
+  <si>
+    <t>inventory-backpack-content</t>
+  </si>
+  <si>
+    <t>Improve Your Gear</t>
+  </si>
+  <si>
+    <t>Return to Inventory</t>
+  </si>
+  <si>
+    <t>side-peek-close</t>
+  </si>
+  <si>
+    <t>Open Equipped Item</t>
+  </si>
+  <si>
+    <t>Item Details</t>
+  </si>
+  <si>
+    <t>item-details</t>
+  </si>
+  <si>
+    <t>Item Stats</t>
+  </si>
+  <si>
+    <t>item-stats</t>
+  </si>
+  <si>
+    <t>Sockets and Gems</t>
+  </si>
+  <si>
+    <t>Open Sets</t>
+  </si>
+  <si>
+    <t>inventory-sets</t>
+  </si>
+  <si>
+    <t>Sets</t>
+  </si>
+  <si>
+    <t>Open Usable / Alchemy</t>
+  </si>
+  <si>
+    <t>inventory-usable</t>
+  </si>
+  <si>
+    <t>Alchemy Items</t>
+  </si>
+  <si>
+    <t>Open Gems</t>
+  </si>
+  <si>
+    <t>inventory-gems</t>
+  </si>
+  <si>
+    <t>Gem Bag</t>
+  </si>
+  <si>
+    <t>Return to Character Sheet</t>
+  </si>
+  <si>
+    <t>character-inventory-close</t>
+  </si>
+  <si>
+    <t>Modified Stat</t>
+  </si>
+  <si>
+    <t>character-modified-stat</t>
+  </si>
+  <si>
+    <t>Stat Breakdown</t>
+  </si>
+  <si>
+    <t>character-stat-breakdown</t>
+  </si>
+  <si>
+    <t>Final Requirement</t>
+  </si>
+  <si>
+    <t>Reach level 10 with STR, DEX, AGI, INT, DUR, CHR, and FOCUS modified values at least 50 through gear and Gems.</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +2832,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:BS2"/>
+  <dimension ref="A1:BW6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="3.4279999732971" customWidth="true" style="0"/>
@@ -1054,73 +2842,73 @@
     <col min="5" max="5" width="255" customWidth="true" style="0"/>
     <col min="6" max="6" width="255" customWidth="true" style="0"/>
     <col min="7" max="7" width="17.566999435425" customWidth="true" style="0"/>
-    <col min="8" max="8" width="35.277000427246" customWidth="true" style="0"/>
-    <col min="9" max="9" width="18.709999084473" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.708000183105" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.420999526978" customWidth="true" style="0"/>
-    <col min="12" max="12" width="36.419998168945" customWidth="true" style="0"/>
-    <col min="13" max="13" width="23.423000335693" customWidth="true" style="0"/>
-    <col min="14" max="14" width="30.563999176025" customWidth="true" style="0"/>
-    <col min="15" max="15" width="38.847999572754" customWidth="true" style="0"/>
-    <col min="16" max="16" width="30.563999176025" customWidth="true" style="0"/>
-    <col min="17" max="17" width="23.423000335693" customWidth="true" style="0"/>
-    <col min="18" max="18" width="26.993000030518" customWidth="true" style="0"/>
-    <col min="19" max="19" width="24.708000183105" customWidth="true" style="0"/>
-    <col min="20" max="20" width="38.847999572754" customWidth="true" style="0"/>
+    <col min="11" max="11" width="35.277000427246" customWidth="true" style="0"/>
+    <col min="12" max="12" width="18.709999084473" customWidth="true" style="0"/>
+    <col min="13" max="13" width="24.708000183105" customWidth="true" style="0"/>
+    <col min="14" max="14" width="29.420999526978" customWidth="true" style="0"/>
+    <col min="15" max="15" width="36.419998168945" customWidth="true" style="0"/>
+    <col min="16" max="16" width="23.423000335693" customWidth="true" style="0"/>
+    <col min="17" max="17" width="30.563999176025" customWidth="true" style="0"/>
+    <col min="18" max="18" width="38.847999572754" customWidth="true" style="0"/>
+    <col min="19" max="19" width="30.563999176025" customWidth="true" style="0"/>
+    <col min="20" max="20" width="23.423000335693" customWidth="true" style="0"/>
     <col min="21" max="21" width="26.993000030518" customWidth="true" style="0"/>
-    <col min="22" max="22" width="28.135999679565" customWidth="true" style="0"/>
-    <col min="23" max="23" width="16.424999237061" customWidth="true" style="0"/>
-    <col min="24" max="24" width="22.280000686646" customWidth="true" style="0"/>
-    <col min="25" max="25" width="18.709999084473" customWidth="true" style="0"/>
-    <col min="26" max="26" width="25.850999832153" customWidth="true" style="0"/>
-    <col min="27" max="27" width="22.280000686646" customWidth="true" style="0"/>
-    <col min="28" max="28" width="21.138000488281" customWidth="true" style="0"/>
-    <col min="29" max="29" width="26.993000030518" customWidth="true" style="0"/>
-    <col min="30" max="30" width="26.993000030518" customWidth="true" style="0"/>
-    <col min="31" max="31" width="34.134998321533" customWidth="true" style="0"/>
-    <col min="32" max="32" width="37.705001831055" customWidth="true" style="0"/>
+    <col min="23" max="23" width="24.708000183105" customWidth="true" style="0"/>
+    <col min="24" max="24" width="38.847999572754" customWidth="true" style="0"/>
+    <col min="25" max="25" width="26.993000030518" customWidth="true" style="0"/>
+    <col min="26" max="26" width="28.135999679565" customWidth="true" style="0"/>
+    <col min="27" max="27" width="16.424999237061" customWidth="true" style="0"/>
+    <col min="28" max="28" width="22.280000686646" customWidth="true" style="0"/>
+    <col min="29" max="29" width="18.709999084473" customWidth="true" style="0"/>
+    <col min="30" max="30" width="25.850999832153" customWidth="true" style="0"/>
+    <col min="31" max="31" width="22.280000686646" customWidth="true" style="0"/>
+    <col min="32" max="32" width="21.138000488281" customWidth="true" style="0"/>
     <col min="33" max="33" width="26.993000030518" customWidth="true" style="0"/>
     <col min="34" max="34" width="26.993000030518" customWidth="true" style="0"/>
-    <col min="35" max="35" width="17.566999435425" customWidth="true" style="0"/>
-    <col min="36" max="36" width="15.281999588013" customWidth="true" style="0"/>
-    <col min="37" max="37" width="15.281999588013" customWidth="true" style="0"/>
-    <col min="38" max="38" width="15.281999588013" customWidth="true" style="0"/>
-    <col min="39" max="39" width="15.281999588013" customWidth="true" style="0"/>
+    <col min="35" max="35" width="34.134998321533" customWidth="true" style="0"/>
+    <col min="36" max="36" width="37.705001831055" customWidth="true" style="0"/>
+    <col min="37" max="37" width="26.993000030518" customWidth="true" style="0"/>
+    <col min="38" max="38" width="26.993000030518" customWidth="true" style="0"/>
+    <col min="39" max="39" width="17.566999435425" customWidth="true" style="0"/>
     <col min="40" max="40" width="15.281999588013" customWidth="true" style="0"/>
     <col min="41" max="41" width="15.281999588013" customWidth="true" style="0"/>
-    <col min="42" max="42" width="17.566999435425" customWidth="true" style="0"/>
-    <col min="43" max="43" width="19.995000839233" customWidth="true" style="0"/>
-    <col min="44" max="44" width="16.424999237061" customWidth="true" style="0"/>
-    <col min="45" max="45" width="13.996999740601" customWidth="true" style="0"/>
-    <col min="46" max="46" width="11.711000442505" customWidth="true" style="0"/>
-    <col min="47" max="47" width="43.561000823975" customWidth="true" style="0"/>
-    <col min="48" max="48" width="18.709999084473" customWidth="true" style="0"/>
-    <col min="49" max="49" width="21.138000488281" customWidth="true" style="0"/>
-    <col min="50" max="50" width="23.423000335693" customWidth="true" style="0"/>
-    <col min="51" max="51" width="39.990001678467" customWidth="true" style="0"/>
-    <col min="52" max="52" width="50.55899810791" customWidth="true" style="0"/>
-    <col min="53" max="53" width="52.986999511719" customWidth="true" style="0"/>
-    <col min="54" max="54" width="24.708000183105" customWidth="true" style="0"/>
-    <col min="55" max="55" width="26.993000030518" customWidth="true" style="0"/>
-    <col min="56" max="56" width="28.135999679565" customWidth="true" style="0"/>
-    <col min="57" max="57" width="23.423000335693" customWidth="true" style="0"/>
-    <col min="58" max="58" width="34.134998321533" customWidth="true" style="0"/>
-    <col min="59" max="59" width="29.420999526978" customWidth="true" style="0"/>
-    <col min="60" max="60" width="34.134998321533" customWidth="true" style="0"/>
-    <col min="61" max="61" width="35.277000427246" customWidth="true" style="0"/>
-    <col min="62" max="62" width="26.993000030518" customWidth="true" style="0"/>
+    <col min="42" max="42" width="15.281999588013" customWidth="true" style="0"/>
+    <col min="43" max="43" width="15.281999588013" customWidth="true" style="0"/>
+    <col min="44" max="44" width="15.281999588013" customWidth="true" style="0"/>
+    <col min="45" max="45" width="15.281999588013" customWidth="true" style="0"/>
+    <col min="46" max="46" width="17.566999435425" customWidth="true" style="0"/>
+    <col min="47" max="47" width="19.995000839233" customWidth="true" style="0"/>
+    <col min="48" max="48" width="16.424999237061" customWidth="true" style="0"/>
+    <col min="49" max="49" width="13.996999740601" customWidth="true" style="0"/>
+    <col min="50" max="50" width="11.711000442505" customWidth="true" style="0"/>
+    <col min="51" max="51" width="43.561000823975" customWidth="true" style="0"/>
+    <col min="52" max="52" width="18.709999084473" customWidth="true" style="0"/>
+    <col min="53" max="53" width="21.138000488281" customWidth="true" style="0"/>
+    <col min="54" max="54" width="23.423000335693" customWidth="true" style="0"/>
+    <col min="55" max="55" width="39.990001678467" customWidth="true" style="0"/>
+    <col min="56" max="56" width="50.55899810791" customWidth="true" style="0"/>
+    <col min="57" max="57" width="52.986999511719" customWidth="true" style="0"/>
+    <col min="58" max="58" width="24.708000183105" customWidth="true" style="0"/>
+    <col min="59" max="59" width="26.993000030518" customWidth="true" style="0"/>
+    <col min="60" max="60" width="28.135999679565" customWidth="true" style="0"/>
+    <col min="61" max="61" width="23.423000335693" customWidth="true" style="0"/>
+    <col min="62" max="62" width="34.134998321533" customWidth="true" style="0"/>
     <col min="63" max="63" width="29.420999526978" customWidth="true" style="0"/>
-    <col min="64" max="64" width="28.135999679565" customWidth="true" style="0"/>
-    <col min="65" max="65" width="26.993000030518" customWidth="true" style="0"/>
-    <col min="66" max="66" width="39.990001678467" customWidth="true" style="0"/>
-    <col min="67" max="67" width="26.993000030518" customWidth="true" style="0"/>
-    <col min="68" max="68" width="24.708000183105" customWidth="true" style="0"/>
-    <col min="69" max="69" width="24.708000183105" customWidth="true" style="0"/>
-    <col min="70" max="70" width="26.993000030518" customWidth="true" style="0"/>
-    <col min="71" max="71" width="39.990001678467" customWidth="true" style="0"/>
+    <col min="64" max="64" width="34.134998321533" customWidth="true" style="0"/>
+    <col min="65" max="65" width="35.277000427246" customWidth="true" style="0"/>
+    <col min="66" max="66" width="26.993000030518" customWidth="true" style="0"/>
+    <col min="67" max="67" width="29.420999526978" customWidth="true" style="0"/>
+    <col min="68" max="68" width="28.135999679565" customWidth="true" style="0"/>
+    <col min="69" max="69" width="26.993000030518" customWidth="true" style="0"/>
+    <col min="70" max="70" width="39.990001678467" customWidth="true" style="0"/>
+    <col min="71" max="71" width="26.993000030518" customWidth="true" style="0"/>
+    <col min="72" max="72" width="24.708000183105" customWidth="true" style="0"/>
+    <col min="73" max="73" width="24.708000183105" customWidth="true" style="0"/>
+    <col min="74" max="74" width="26.993000030518" customWidth="true" style="0"/>
+    <col min="75" max="75" width="39.990001678467" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71">
+    <row r="1" spans="1:75">
       <c r="A1" t="inlineStr">
         <is>
           <r>
@@ -1233,7 +3021,16 @@
           </r>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1249,7 +3046,7 @@
           </r>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1265,7 +3062,7 @@
           </r>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1281,7 +3078,7 @@
           </r>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1297,7 +3094,7 @@
           </r>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1313,7 +3110,7 @@
           </r>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1329,7 +3126,7 @@
           </r>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1345,7 +3142,7 @@
           </r>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1361,7 +3158,7 @@
           </r>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1377,7 +3174,7 @@
           </r>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1393,7 +3190,7 @@
           </r>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1409,7 +3206,10 @@
           </r>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1425,7 +3225,7 @@
           </r>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1441,7 +3241,7 @@
           </r>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1457,7 +3257,7 @@
           </r>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1473,7 +3273,7 @@
           </r>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1489,7 +3289,7 @@
           </r>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1505,7 +3305,7 @@
           </r>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1521,7 +3321,7 @@
           </r>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1537,7 +3337,7 @@
           </r>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1553,7 +3353,7 @@
           </r>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1569,7 +3369,7 @@
           </r>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1585,7 +3385,7 @@
           </r>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1601,7 +3401,7 @@
           </r>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1617,7 +3417,7 @@
           </r>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1633,7 +3433,7 @@
           </r>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1649,7 +3449,7 @@
           </r>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1665,7 +3465,7 @@
           </r>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1681,7 +3481,7 @@
           </r>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1697,7 +3497,7 @@
           </r>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1713,7 +3513,7 @@
           </r>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1729,7 +3529,7 @@
           </r>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1745,7 +3545,7 @@
           </r>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1761,7 +3561,7 @@
           </r>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1777,7 +3577,7 @@
           </r>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1793,7 +3593,7 @@
           </r>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1809,7 +3609,7 @@
           </r>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1825,7 +3625,7 @@
           </r>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1841,7 +3641,7 @@
           </r>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1857,7 +3657,7 @@
           </r>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1873,7 +3673,7 @@
           </r>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1889,7 +3689,7 @@
           </r>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1905,7 +3705,7 @@
           </r>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1921,7 +3721,7 @@
           </r>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1937,7 +3737,7 @@
           </r>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1953,7 +3753,7 @@
           </r>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1969,7 +3769,7 @@
           </r>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1985,7 +3785,7 @@
           </r>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2001,7 +3801,7 @@
           </r>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2017,7 +3817,7 @@
           </r>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2033,7 +3833,7 @@
           </r>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2049,7 +3849,7 @@
           </r>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2065,7 +3865,7 @@
           </r>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2081,7 +3881,7 @@
           </r>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2097,7 +3897,7 @@
           </r>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2113,7 +3913,7 @@
           </r>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2129,7 +3929,7 @@
           </r>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2145,7 +3945,7 @@
           </r>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2161,7 +3961,7 @@
           </r>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2177,7 +3977,7 @@
           </r>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2193,7 +3993,7 @@
           </r>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2209,7 +4009,7 @@
           </r>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2225,7 +4025,7 @@
           </r>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2241,7 +4041,7 @@
           </r>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2258,7 +4058,7 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:71">
+    <row r="2" spans="1:75">
       <c r="B2" t="inlineStr">
         <is>
           <r>
@@ -2342,11 +4142,124 @@
       <c r="G2">
         <v>2</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>100</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:75">
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:75">
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4">
+        <v>0.1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>91</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="AX4">
+        <v>20</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:75">
+      <c r="B5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" t="s">
+        <v>96</v>
+      </c>
+      <c r="T5" t="s">
+        <v>97</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>25</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:75">
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="AM6">
+        <v>50</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2361,7 +4274,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4024,22 +5937,22 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="E19" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="F19" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -4047,22 +5960,22 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="F20" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -4070,25 +5983,25 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="E21" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="F21" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="G21" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -4096,22 +6009,22 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="D22" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="E22" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -4119,21 +6032,1515 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="F23" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" t="s">
+        <v>184</v>
+      </c>
+      <c r="E24" t="s">
+        <v>185</v>
+      </c>
+      <c r="F24" t="s">
+        <v>186</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" t="s">
+        <v>189</v>
+      </c>
+      <c r="F25" t="s">
+        <v>169</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" t="s">
+        <v>191</v>
+      </c>
+      <c r="E26" t="s">
+        <v>192</v>
+      </c>
+      <c r="F26" t="s">
+        <v>186</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>193</v>
+      </c>
+      <c r="D27" t="s">
+        <v>194</v>
+      </c>
+      <c r="E27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F27" t="s">
+        <v>186</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" t="s">
+        <v>197</v>
+      </c>
+      <c r="E28" t="s">
+        <v>198</v>
+      </c>
+      <c r="F28" t="s">
+        <v>186</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29" t="s">
+        <v>200</v>
+      </c>
+      <c r="E29" t="s">
+        <v>201</v>
+      </c>
+      <c r="F29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" t="s">
+        <v>203</v>
+      </c>
+      <c r="E30" t="s">
+        <v>204</v>
+      </c>
+      <c r="F30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>205</v>
+      </c>
+      <c r="D31" t="s">
+        <v>206</v>
+      </c>
+      <c r="E31" t="s">
+        <v>207</v>
+      </c>
+      <c r="F31" t="s">
+        <v>186</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>208</v>
+      </c>
+      <c r="D32" t="s">
+        <v>209</v>
+      </c>
+      <c r="E32" t="s">
+        <v>210</v>
+      </c>
+      <c r="F32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>211</v>
+      </c>
+      <c r="D33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" t="s">
+        <v>213</v>
+      </c>
+      <c r="F33" t="s">
+        <v>186</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>214</v>
+      </c>
+      <c r="D34" t="s">
+        <v>215</v>
+      </c>
+      <c r="E34" t="s">
+        <v>216</v>
+      </c>
+      <c r="F34" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>217</v>
+      </c>
+      <c r="D35" t="s">
+        <v>218</v>
+      </c>
+      <c r="F35" t="s">
+        <v>169</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>219</v>
+      </c>
+      <c r="D36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" t="s">
+        <v>221</v>
+      </c>
+      <c r="F36" t="s">
+        <v>186</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>222</v>
+      </c>
+      <c r="D37" t="s">
+        <v>223</v>
+      </c>
+      <c r="E37" t="s">
+        <v>224</v>
+      </c>
+      <c r="F37" t="s">
+        <v>169</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>225</v>
+      </c>
+      <c r="D38" t="s">
+        <v>226</v>
+      </c>
+      <c r="E38" t="s">
+        <v>227</v>
+      </c>
+      <c r="F38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>228</v>
+      </c>
+      <c r="D39" t="s">
+        <v>229</v>
+      </c>
+      <c r="E39" t="s">
+        <v>230</v>
+      </c>
+      <c r="F39" t="s">
+        <v>169</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40">
+        <v>5</v>
+      </c>
+      <c r="C40" t="s">
+        <v>231</v>
+      </c>
+      <c r="D40" t="s">
+        <v>232</v>
+      </c>
+      <c r="E40" t="s">
+        <v>233</v>
+      </c>
+      <c r="F40" t="s">
+        <v>186</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>234</v>
+      </c>
+      <c r="D41" t="s">
+        <v>235</v>
+      </c>
+      <c r="E41" t="s">
+        <v>236</v>
+      </c>
+      <c r="F41" t="s">
+        <v>169</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>237</v>
+      </c>
+      <c r="D42" t="s">
+        <v>238</v>
+      </c>
+      <c r="E42" t="s">
+        <v>239</v>
+      </c>
+      <c r="F42" t="s">
+        <v>169</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>240</v>
+      </c>
+      <c r="D43" t="s">
+        <v>241</v>
+      </c>
+      <c r="E43" t="s">
+        <v>242</v>
+      </c>
+      <c r="F43" t="s">
+        <v>186</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" t="s">
+        <v>243</v>
+      </c>
+      <c r="E44" t="s">
+        <v>244</v>
+      </c>
+      <c r="F44" t="s">
+        <v>169</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>245</v>
+      </c>
+      <c r="D45" t="s">
+        <v>246</v>
+      </c>
+      <c r="E45" t="s">
+        <v>247</v>
+      </c>
+      <c r="F45" t="s">
+        <v>169</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46">
+        <v>11</v>
+      </c>
+      <c r="C46" t="s">
+        <v>248</v>
+      </c>
+      <c r="D46" t="s">
+        <v>249</v>
+      </c>
+      <c r="E46" t="s">
+        <v>250</v>
+      </c>
+      <c r="F46" t="s">
+        <v>186</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>251</v>
+      </c>
+      <c r="D47" t="s">
+        <v>252</v>
+      </c>
+      <c r="E47" t="s">
+        <v>253</v>
+      </c>
+      <c r="F47" t="s">
+        <v>169</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48">
+        <v>13</v>
+      </c>
+      <c r="C48" t="s">
+        <v>254</v>
+      </c>
+      <c r="D48" t="s">
+        <v>255</v>
+      </c>
+      <c r="E48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F48" t="s">
+        <v>176</v>
+      </c>
+      <c r="G48" t="s">
+        <v>257</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s">
+        <v>258</v>
+      </c>
+      <c r="D49" t="s">
+        <v>259</v>
+      </c>
+      <c r="E49" t="s">
+        <v>244</v>
+      </c>
+      <c r="F49" t="s">
+        <v>169</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50">
+        <v>15</v>
+      </c>
+      <c r="C50" t="s">
+        <v>260</v>
+      </c>
+      <c r="D50" t="s">
+        <v>261</v>
+      </c>
+      <c r="E50" t="s">
+        <v>262</v>
+      </c>
+      <c r="F50" t="s">
+        <v>169</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51">
+        <v>16</v>
+      </c>
+      <c r="C51" t="s">
+        <v>263</v>
+      </c>
+      <c r="D51" t="s">
+        <v>264</v>
+      </c>
+      <c r="E51" t="s">
+        <v>265</v>
+      </c>
+      <c r="F51" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52">
+        <v>17</v>
+      </c>
+      <c r="C52" t="s">
+        <v>266</v>
+      </c>
+      <c r="D52" t="s">
+        <v>267</v>
+      </c>
+      <c r="E52" t="s">
+        <v>268</v>
+      </c>
+      <c r="F52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53">
+        <v>18</v>
+      </c>
+      <c r="C53" t="s">
+        <v>269</v>
+      </c>
+      <c r="D53" t="s">
+        <v>270</v>
+      </c>
+      <c r="E53" t="s">
+        <v>271</v>
+      </c>
+      <c r="F53" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54">
+        <v>19</v>
+      </c>
+      <c r="C54" t="s">
+        <v>272</v>
+      </c>
+      <c r="D54" t="s">
+        <v>273</v>
+      </c>
+      <c r="F54" t="s">
+        <v>169</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>274</v>
+      </c>
+      <c r="D55" t="s">
+        <v>275</v>
+      </c>
+      <c r="E55" t="s">
+        <v>276</v>
+      </c>
+      <c r="F55" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56">
+        <v>2</v>
+      </c>
+      <c r="C56" t="s">
+        <v>277</v>
+      </c>
+      <c r="D56" t="s">
+        <v>278</v>
+      </c>
+      <c r="E56" t="s">
+        <v>279</v>
+      </c>
+      <c r="F56" t="s">
+        <v>186</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>92</v>
+      </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
+        <v>280</v>
+      </c>
+      <c r="D57" t="s">
+        <v>281</v>
+      </c>
+      <c r="E57" t="s">
+        <v>282</v>
+      </c>
+      <c r="F57" t="s">
+        <v>169</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B58">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>283</v>
+      </c>
+      <c r="D58" t="s">
+        <v>284</v>
+      </c>
+      <c r="E58" t="s">
+        <v>285</v>
+      </c>
+      <c r="F58" t="s">
+        <v>186</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59">
+        <v>5</v>
+      </c>
+      <c r="C59" t="s">
+        <v>286</v>
+      </c>
+      <c r="D59" t="s">
+        <v>287</v>
+      </c>
+      <c r="E59" t="s">
+        <v>288</v>
+      </c>
+      <c r="F59" t="s">
+        <v>169</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>289</v>
+      </c>
+      <c r="D60" t="s">
+        <v>290</v>
+      </c>
+      <c r="E60" t="s">
+        <v>291</v>
+      </c>
+      <c r="F60" t="s">
+        <v>186</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>292</v>
+      </c>
+      <c r="D61" t="s">
+        <v>293</v>
+      </c>
+      <c r="E61" t="s">
+        <v>207</v>
+      </c>
+      <c r="F61" t="s">
+        <v>186</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>92</v>
+      </c>
+      <c r="B62">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
+        <v>294</v>
+      </c>
+      <c r="D62" t="s">
+        <v>295</v>
+      </c>
+      <c r="E62" t="s">
+        <v>296</v>
+      </c>
+      <c r="F62" t="s">
+        <v>169</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63">
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
+        <v>297</v>
+      </c>
+      <c r="D63" t="s">
+        <v>298</v>
+      </c>
+      <c r="F63" t="s">
+        <v>169</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>98</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>219</v>
+      </c>
+      <c r="D64" t="s">
+        <v>299</v>
+      </c>
+      <c r="E64" t="s">
+        <v>221</v>
+      </c>
+      <c r="F64" t="s">
+        <v>186</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>300</v>
+      </c>
+      <c r="D65" t="s">
+        <v>299</v>
+      </c>
+      <c r="E65" t="s">
+        <v>301</v>
+      </c>
+      <c r="F65" t="s">
+        <v>186</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>98</v>
+      </c>
+      <c r="B66">
+        <v>3</v>
+      </c>
+      <c r="C66" t="s">
+        <v>302</v>
+      </c>
+      <c r="D66" t="s">
+        <v>299</v>
+      </c>
+      <c r="E66" t="s">
+        <v>303</v>
+      </c>
+      <c r="F66" t="s">
+        <v>169</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>98</v>
+      </c>
+      <c r="B67">
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
+        <v>304</v>
+      </c>
+      <c r="D67" t="s">
+        <v>299</v>
+      </c>
+      <c r="E67" t="s">
+        <v>305</v>
+      </c>
+      <c r="F67" t="s">
+        <v>169</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>98</v>
+      </c>
+      <c r="B68">
+        <v>5</v>
+      </c>
+      <c r="C68" t="s">
+        <v>306</v>
+      </c>
+      <c r="D68" t="s">
+        <v>299</v>
+      </c>
+      <c r="E68" t="s">
+        <v>307</v>
+      </c>
+      <c r="F68" t="s">
+        <v>186</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>98</v>
+      </c>
+      <c r="B69">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>308</v>
+      </c>
+      <c r="D69" t="s">
+        <v>299</v>
+      </c>
+      <c r="E69" t="s">
+        <v>309</v>
+      </c>
+      <c r="F69" t="s">
+        <v>169</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70">
+        <v>7</v>
+      </c>
+      <c r="C70" t="s">
+        <v>310</v>
+      </c>
+      <c r="D70" t="s">
+        <v>299</v>
+      </c>
+      <c r="F70" t="s">
+        <v>169</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>98</v>
+      </c>
+      <c r="B71">
+        <v>8</v>
+      </c>
+      <c r="C71" t="s">
+        <v>311</v>
+      </c>
+      <c r="D71" t="s">
+        <v>299</v>
+      </c>
+      <c r="E71" t="s">
+        <v>312</v>
+      </c>
+      <c r="F71" t="s">
+        <v>186</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>98</v>
+      </c>
+      <c r="B72">
+        <v>9</v>
+      </c>
+      <c r="C72" t="s">
+        <v>313</v>
+      </c>
+      <c r="D72" t="s">
+        <v>299</v>
+      </c>
+      <c r="E72" t="s">
+        <v>305</v>
+      </c>
+      <c r="F72" t="s">
+        <v>186</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>98</v>
+      </c>
+      <c r="B73">
+        <v>10</v>
+      </c>
+      <c r="C73" t="s">
+        <v>314</v>
+      </c>
+      <c r="D73" t="s">
+        <v>299</v>
+      </c>
+      <c r="E73" t="s">
+        <v>315</v>
+      </c>
+      <c r="F73" t="s">
+        <v>169</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>98</v>
+      </c>
+      <c r="B74">
+        <v>11</v>
+      </c>
+      <c r="C74" t="s">
+        <v>316</v>
+      </c>
+      <c r="D74" t="s">
+        <v>299</v>
+      </c>
+      <c r="E74" t="s">
+        <v>317</v>
+      </c>
+      <c r="F74" t="s">
+        <v>169</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>98</v>
+      </c>
+      <c r="B75">
+        <v>12</v>
+      </c>
+      <c r="C75" t="s">
+        <v>318</v>
+      </c>
+      <c r="D75" t="s">
+        <v>299</v>
+      </c>
+      <c r="F75" t="s">
+        <v>169</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>98</v>
+      </c>
+      <c r="B76">
+        <v>13</v>
+      </c>
+      <c r="C76" t="s">
+        <v>311</v>
+      </c>
+      <c r="D76" t="s">
+        <v>299</v>
+      </c>
+      <c r="E76" t="s">
+        <v>312</v>
+      </c>
+      <c r="F76" t="s">
+        <v>186</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>98</v>
+      </c>
+      <c r="B77">
+        <v>14</v>
+      </c>
+      <c r="C77" t="s">
+        <v>319</v>
+      </c>
+      <c r="D77" t="s">
+        <v>299</v>
+      </c>
+      <c r="E77" t="s">
+        <v>320</v>
+      </c>
+      <c r="F77" t="s">
+        <v>186</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>98</v>
+      </c>
+      <c r="B78">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
+        <v>321</v>
+      </c>
+      <c r="D78" t="s">
+        <v>299</v>
+      </c>
+      <c r="F78" t="s">
+        <v>169</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>98</v>
+      </c>
+      <c r="B79">
+        <v>16</v>
+      </c>
+      <c r="C79" t="s">
+        <v>311</v>
+      </c>
+      <c r="D79" t="s">
+        <v>299</v>
+      </c>
+      <c r="E79" t="s">
+        <v>312</v>
+      </c>
+      <c r="F79" t="s">
+        <v>186</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>98</v>
+      </c>
+      <c r="B80">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>322</v>
+      </c>
+      <c r="D80" t="s">
+        <v>299</v>
+      </c>
+      <c r="E80" t="s">
+        <v>323</v>
+      </c>
+      <c r="F80" t="s">
+        <v>186</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81">
+        <v>18</v>
+      </c>
+      <c r="C81" t="s">
+        <v>324</v>
+      </c>
+      <c r="D81" t="s">
+        <v>299</v>
+      </c>
+      <c r="F81" t="s">
+        <v>169</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>98</v>
+      </c>
+      <c r="B82">
+        <v>19</v>
+      </c>
+      <c r="C82" t="s">
+        <v>311</v>
+      </c>
+      <c r="D82" t="s">
+        <v>299</v>
+      </c>
+      <c r="E82" t="s">
+        <v>312</v>
+      </c>
+      <c r="F82" t="s">
+        <v>186</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83">
+        <v>20</v>
+      </c>
+      <c r="C83" t="s">
+        <v>325</v>
+      </c>
+      <c r="D83" t="s">
+        <v>299</v>
+      </c>
+      <c r="E83" t="s">
+        <v>326</v>
+      </c>
+      <c r="F83" t="s">
+        <v>186</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>98</v>
+      </c>
+      <c r="B84">
+        <v>21</v>
+      </c>
+      <c r="C84" t="s">
+        <v>327</v>
+      </c>
+      <c r="D84" t="s">
+        <v>299</v>
+      </c>
+      <c r="F84" t="s">
+        <v>169</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>98</v>
+      </c>
+      <c r="B85">
+        <v>22</v>
+      </c>
+      <c r="C85" t="s">
+        <v>311</v>
+      </c>
+      <c r="D85" t="s">
+        <v>299</v>
+      </c>
+      <c r="E85" t="s">
+        <v>312</v>
+      </c>
+      <c r="F85" t="s">
+        <v>186</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>98</v>
+      </c>
+      <c r="B86">
+        <v>23</v>
+      </c>
+      <c r="C86" t="s">
+        <v>328</v>
+      </c>
+      <c r="D86" t="s">
+        <v>299</v>
+      </c>
+      <c r="E86" t="s">
+        <v>329</v>
+      </c>
+      <c r="F86" t="s">
+        <v>186</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>98</v>
+      </c>
+      <c r="B87">
+        <v>24</v>
+      </c>
+      <c r="C87" t="s">
+        <v>330</v>
+      </c>
+      <c r="D87" t="s">
+        <v>299</v>
+      </c>
+      <c r="E87" t="s">
+        <v>331</v>
+      </c>
+      <c r="F87" t="s">
+        <v>186</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88">
+        <v>25</v>
+      </c>
+      <c r="C88" t="s">
+        <v>332</v>
+      </c>
+      <c r="D88" t="s">
+        <v>299</v>
+      </c>
+      <c r="E88" t="s">
+        <v>333</v>
+      </c>
+      <c r="F88" t="s">
+        <v>169</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>98</v>
+      </c>
+      <c r="B89">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
+        <v>334</v>
+      </c>
+      <c r="D89" t="s">
+        <v>335</v>
+      </c>
+      <c r="F89" t="s">
+        <v>169</v>
+      </c>
+      <c r="H89">
         <v>0</v>
       </c>
     </row>
